--- a/jogos_2024-11-11.xlsx
+++ b/jogos_2024-11-11.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -643,109 +643,109 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nakhon Pathom</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="M2" t="n">
         <v>3</v>
       </c>
-      <c r="H2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L2" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="M2" t="n">
-        <v>4.4</v>
-      </c>
       <c r="N2" t="n">
-        <v>6.5</v>
+        <v>3.1</v>
       </c>
       <c r="O2" t="n">
-        <v>1.81</v>
+        <v>2.88</v>
       </c>
       <c r="P2" t="n">
-        <v>2.55</v>
+        <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.8</v>
+        <v>3.75</v>
       </c>
       <c r="R2" t="n">
-        <v>1.24</v>
+        <v>1.43</v>
       </c>
       <c r="S2" t="n">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
       <c r="T2" t="n">
-        <v>2.19</v>
+        <v>3</v>
       </c>
       <c r="U2" t="n">
-        <v>1.62</v>
+        <v>1.34</v>
       </c>
       <c r="V2" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="W2" t="n">
-        <v>1.11</v>
+        <v>1.36</v>
       </c>
       <c r="X2" t="n">
-        <v>5.5</v>
+        <v>2.88</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.41</v>
+        <v>1.65</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.3</v>
+        <v>4</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.55</v>
+        <v>1.2</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="AD2" t="n">
-        <v>2.03</v>
+        <v>1.8</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>['45+2', '90+17', '90+20']</t>
+          <t>['81']</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>['90+10']</t>
+          <t>['87', '89']</t>
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.09</v>
+        <v>1.34</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.36</v>
+        <v>1.58</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.36</v>
+        <v>1.8</v>
       </c>
       <c r="AJ2" t="n">
-        <v>3.3</v>
+        <v>2.4</v>
       </c>
       <c r="AK2" s="3" t="n">
         <v>45607.375</v>
@@ -772,69 +772,69 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Mladost Novi Sad</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H3" t="n">
         <v>1</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>2</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>1</v>
       </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.9</v>
+        <v>1.99</v>
       </c>
       <c r="M3" t="n">
-        <v>2.72</v>
+        <v>2.85</v>
       </c>
       <c r="N3" t="n">
-        <v>2.45</v>
+        <v>3.75</v>
       </c>
       <c r="O3" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="P3" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="R3" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="S3" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="T3" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="U3" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="V3" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="W3" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="X3" t="n">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="Y3" t="n">
         <v>2.48</v>
@@ -843,38 +843,38 @@
         <v>1.48</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AC3" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>['14']</t>
+          <t>['13', '34', '75']</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>['50', '90+6']</t>
+          <t>['21']</t>
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.45</v>
+        <v>1.19</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.47</v>
+        <v>1.93</v>
       </c>
       <c r="AI3" t="n">
-        <v>2.05</v>
+        <v>1.5</v>
       </c>
       <c r="AJ3" t="n">
-        <v>2.05</v>
+        <v>3.25</v>
       </c>
       <c r="AK3" s="3" t="n">
         <v>45607.375</v>
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Mladost Novi Sad</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Nakhon Pathom</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -916,10 +916,10 @@
         <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -927,83 +927,83 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.99</v>
+        <v>1.4</v>
       </c>
       <c r="M4" t="n">
-        <v>2.85</v>
+        <v>4.4</v>
       </c>
       <c r="N4" t="n">
-        <v>3.75</v>
+        <v>6.5</v>
       </c>
       <c r="O4" t="n">
-        <v>2.4</v>
+        <v>1.81</v>
       </c>
       <c r="P4" t="n">
-        <v>2</v>
+        <v>2.55</v>
       </c>
       <c r="Q4" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="R4" t="n">
-        <v>1.46</v>
+        <v>1.24</v>
       </c>
       <c r="S4" t="n">
-        <v>2.5</v>
+        <v>3.6</v>
       </c>
       <c r="T4" t="n">
-        <v>3.1</v>
+        <v>2.19</v>
       </c>
       <c r="U4" t="n">
-        <v>1.31</v>
+        <v>1.62</v>
       </c>
       <c r="V4" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="W4" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>['45+2', '90+17', '90+20']</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>['90+10']</t>
+        </is>
+      </c>
+      <c r="AG4" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AI4" t="n">
         <v>1.36</v>
       </c>
-      <c r="X4" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>['13', '34', '75']</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>['21']</t>
-        </is>
-      </c>
-      <c r="AG4" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AJ4" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45607.375</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1045,7 +1045,7 @@
         <v>2</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -1056,83 +1056,83 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="M5" t="n">
-        <v>3</v>
+        <v>2.72</v>
       </c>
       <c r="N5" t="n">
-        <v>3.1</v>
+        <v>2.45</v>
       </c>
       <c r="O5" t="n">
-        <v>2.88</v>
+        <v>3.4</v>
       </c>
       <c r="P5" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X5" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AC5" t="n">
         <v>2</v>
       </c>
-      <c r="Q5" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T5" t="n">
-        <v>3</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X5" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AD5" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>['81']</t>
+          <t>['14']</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>['87', '89']</t>
+          <t>['50', '90+6']</t>
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.34</v>
+        <v>1.45</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.58</v>
+        <v>1.47</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="AJ5" t="n">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45607.375</v>
@@ -1804,19 +1804,19 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hapoel Umm al-Fahm</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -1830,83 +1830,83 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.8</v>
+        <v>1.83</v>
       </c>
       <c r="M11" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="N11" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O11" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="X11" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Y11" t="n">
         <v>2.25</v>
       </c>
-      <c r="O11" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q11" t="n">
+      <c r="Z11" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>['67']</t>
+        </is>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AJ11" t="n">
         <v>2.88</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="X11" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1.8</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45607.58333333334</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,109 +1933,109 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Hapoel Umm al-Fahm</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Igman Konjic</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
       </c>
       <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="M12" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N12" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="O12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="X12" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD12" t="n">
         <v>2</v>
       </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L12" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="M12" t="n">
-        <v>4.69</v>
-      </c>
-      <c r="N12" t="n">
-        <v>7.93</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="P12" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S12" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X12" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="Z12" t="n">
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI12" t="n">
         <v>2.2</v>
       </c>
-      <c r="AA12" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>['14', '45', '69', '73']</t>
-        </is>
-      </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AJ12" t="n">
-        <v>4.33</v>
+        <v>1.8</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45607.58333333334</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,22 +2062,22 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Igman Konjic</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -2088,55 +2088,55 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.83</v>
+        <v>1.25</v>
       </c>
       <c r="M13" t="n">
-        <v>3.1</v>
+        <v>4.69</v>
       </c>
       <c r="N13" t="n">
-        <v>4.1</v>
+        <v>7.93</v>
       </c>
       <c r="O13" t="n">
-        <v>2.6</v>
+        <v>1.73</v>
       </c>
       <c r="P13" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
       <c r="R13" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="S13" t="n">
-        <v>2.5</v>
+        <v>3.4</v>
       </c>
       <c r="T13" t="n">
-        <v>3.4</v>
+        <v>2.38</v>
       </c>
       <c r="U13" t="n">
-        <v>1.3</v>
+        <v>1.53</v>
       </c>
       <c r="V13" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="W13" t="n">
-        <v>1.37</v>
+        <v>1.14</v>
       </c>
       <c r="X13" t="n">
-        <v>2.88</v>
+        <v>4.15</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.25</v>
+        <v>1.55</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.62</v>
+        <v>2.2</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.9</v>
+        <v>2.35</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.21</v>
+        <v>1.53</v>
       </c>
       <c r="AC13" t="n">
         <v>2</v>
@@ -2146,25 +2146,25 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
+          <t>['14', '45', '69', '73']</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF13" t="inlineStr">
-        <is>
-          <t>['67']</t>
-        </is>
-      </c>
       <c r="AG13" t="n">
-        <v>1.31</v>
+        <v>1.02</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.47</v>
+        <v>3.4</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.57</v>
+        <v>1.22</v>
       </c>
       <c r="AJ13" t="n">
-        <v>2.88</v>
+        <v>4.33</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45607.58333333334</v>
@@ -2181,26 +2181,26 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Argentina Primera División</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Deportivo Riestra</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vélez Sarsfield</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
         <v>1</v>
@@ -2217,83 +2217,83 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>6.5</v>
+        <v>2.86</v>
       </c>
       <c r="M14" t="n">
-        <v>3.9</v>
+        <v>2.86</v>
       </c>
       <c r="N14" t="n">
-        <v>1.55</v>
+        <v>2.17</v>
       </c>
       <c r="O14" t="n">
-        <v>7</v>
+        <v>3.75</v>
       </c>
       <c r="P14" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="X14" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AC14" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q14" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T14" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="X14" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>2.38</v>
-      </c>
       <c r="AD14" t="n">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>['65']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>['45']</t>
+          <t>['18']</t>
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>2.2</v>
+        <v>1.57</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.16</v>
+        <v>1.33</v>
       </c>
       <c r="AI14" t="n">
-        <v>3.75</v>
+        <v>2.44</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.36</v>
+        <v>1.99</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45607.66666666666</v>
@@ -2310,26 +2310,26 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Argentina Primera División</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Deportivo Riestra</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Vélez Sarsfield</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15" t="n">
         <v>1</v>
@@ -2346,83 +2346,83 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.86</v>
+        <v>6.5</v>
       </c>
       <c r="M15" t="n">
-        <v>2.86</v>
+        <v>3.9</v>
       </c>
       <c r="N15" t="n">
-        <v>2.17</v>
+        <v>1.55</v>
       </c>
       <c r="O15" t="n">
+        <v>7</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X15" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>['65']</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>['45']</t>
+        </is>
+      </c>
+      <c r="AG15" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AI15" t="n">
         <v>3.75</v>
       </c>
-      <c r="P15" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="T15" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="X15" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>['18']</t>
-        </is>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>2.44</v>
-      </c>
       <c r="AJ15" t="n">
-        <v>1.99</v>
+        <v>1.36</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45607.66666666666</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,22 +2449,22 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Turris Neapolis</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H16" t="n">
         <v>1</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2475,83 +2475,83 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.8</v>
+        <v>1.53</v>
       </c>
       <c r="M16" t="n">
-        <v>2.74</v>
+        <v>3.53</v>
       </c>
       <c r="N16" t="n">
-        <v>2.65</v>
+        <v>6.23</v>
       </c>
       <c r="O16" t="n">
+        <v>2</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T16" t="n">
         <v>3.4</v>
       </c>
-      <c r="P16" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3.75</v>
-      </c>
       <c r="U16" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="V16" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X16" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>['11', '44']</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>['75']</t>
+        </is>
+      </c>
+      <c r="AG16" t="n">
         <v>1.05</v>
       </c>
-      <c r="W16" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="X16" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>['82']</t>
-        </is>
-      </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>['58']</t>
-        </is>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AH16" t="n">
-        <v>1.35</v>
+        <v>2.34</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.95</v>
+        <v>1.3</v>
       </c>
       <c r="AJ16" t="n">
-        <v>2.2</v>
+        <v>4.5</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45607.6875</v>
@@ -2578,19 +2578,19 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Taranto</t>
+          <t>Turris Neapolis</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G17" t="n">
         <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -2604,83 +2604,83 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>5.76</v>
+        <v>2.8</v>
       </c>
       <c r="M17" t="n">
-        <v>3.49</v>
+        <v>2.74</v>
       </c>
       <c r="N17" t="n">
-        <v>1.57</v>
+        <v>2.65</v>
       </c>
       <c r="O17" t="n">
-        <v>5.5</v>
+        <v>3.4</v>
       </c>
       <c r="P17" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.3</v>
+        <v>3.5</v>
       </c>
       <c r="R17" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="S17" t="n">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="T17" t="n">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="U17" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="V17" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W17" t="n">
-        <v>1.32</v>
+        <v>1.43</v>
       </c>
       <c r="X17" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.12</v>
+        <v>2.49</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.7</v>
+        <v>1.52</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.66</v>
+        <v>3.85</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>['88']</t>
+          <t>['82']</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['58']</t>
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.11</v>
+        <v>1.35</v>
       </c>
       <c r="AI17" t="n">
-        <v>3.5</v>
+        <v>1.95</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.44</v>
+        <v>2.2</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45607.6875</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,109 +2836,109 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Taranto</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>5.76</v>
+      </c>
+      <c r="M19" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="O19" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="P19" t="n">
         <v>2</v>
       </c>
-      <c r="H19" t="n">
-        <v>1</v>
-      </c>
-      <c r="I19" t="n">
-        <v>2</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L19" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="M19" t="n">
-        <v>3.53</v>
-      </c>
-      <c r="N19" t="n">
-        <v>6.23</v>
-      </c>
-      <c r="O19" t="n">
-        <v>2</v>
-      </c>
-      <c r="P19" t="n">
-        <v>2.1</v>
-      </c>
       <c r="Q19" t="n">
-        <v>7.5</v>
+        <v>2.3</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="S19" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="T19" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="U19" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="V19" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="W19" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="X19" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.31</v>
+        <v>2.12</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="AA19" t="n">
-        <v>4.5</v>
+        <v>3.66</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.63</v>
+        <v>2.25</v>
       </c>
       <c r="AD19" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>['88']</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG19" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AJ19" t="n">
         <v>1.44</v>
-      </c>
-      <c r="AE19" t="inlineStr">
-        <is>
-          <t>['11', '44']</t>
-        </is>
-      </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t>['75']</t>
-        </is>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>4.5</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45607.6875</v>
@@ -3094,19 +3094,19 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Tigre</t>
+          <t>Lanús</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Defensa y Justicia</t>
+          <t>Platense</t>
         </is>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -3120,83 +3120,83 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="M21" t="n">
-        <v>3.25</v>
+        <v>2.88</v>
       </c>
       <c r="N21" t="n">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="O21" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="P21" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="Q21" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="T21" t="n">
         <v>3.75</v>
       </c>
-      <c r="R21" t="n">
+      <c r="U21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="X21" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD21" t="n">
         <v>1.5</v>
       </c>
-      <c r="S21" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T21" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="X21" t="n">
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG21" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ21" t="n">
         <v>2.75</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AE21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF21" t="inlineStr">
-        <is>
-          <t>['68', '71', '80', '90+1']</t>
-        </is>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>2.38</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45607.78125</v>
@@ -3223,19 +3223,19 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Lanús</t>
+          <t>Tigre</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Platense</t>
+          <t>Defensa y Justicia</t>
         </is>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="M22" t="n">
-        <v>2.88</v>
+        <v>3.25</v>
       </c>
       <c r="N22" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O22" t="n">
+        <v>3</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q22" t="n">
         <v>3.75</v>
       </c>
-      <c r="O22" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="P22" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Q22" t="n">
+      <c r="R22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X22" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AA22" t="n">
         <v>4.75</v>
       </c>
-      <c r="R22" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="T22" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="X22" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>6.75</v>
-      </c>
       <c r="AB22" t="n">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.5</v>
+        <v>1.91</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.5</v>
+        <v>1.91</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3312,20 +3312,20 @@
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['68', '71', '80', '90+1']</t>
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AI22" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AJ22" t="n">
-        <v>2.75</v>
+        <v>2.38</v>
       </c>
       <c r="AK22" s="3" t="n">
         <v>45607.78125</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Primera División</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,25 +3610,25 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Argentinos Juniors</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Banfield</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -3636,83 +3636,83 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.91</v>
+        <v>1.73</v>
       </c>
       <c r="M25" t="n">
-        <v>2.88</v>
+        <v>3.3</v>
       </c>
       <c r="N25" t="n">
-        <v>2.66</v>
+        <v>5.75</v>
       </c>
       <c r="O25" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="P25" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.25</v>
+        <v>6</v>
       </c>
       <c r="R25" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W25" t="n">
         <v>1.5</v>
       </c>
-      <c r="S25" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T25" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.49</v>
-      </c>
       <c r="X25" t="n">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AA25" t="n">
-        <v>4.25</v>
+        <v>5.6</v>
       </c>
       <c r="AB25" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>['21']</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG25" t="n">
         <v>1.19</v>
       </c>
-      <c r="AC25" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AE25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF25" t="inlineStr">
-        <is>
-          <t>['20', '41']</t>
-        </is>
-      </c>
-      <c r="AG25" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AH25" t="n">
-        <v>1.42</v>
+        <v>1.96</v>
       </c>
       <c r="AI25" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.83</v>
+        <v>3.5</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45607.875</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Argentina Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Argentinos Juniors</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Banfield</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3754,7 +3754,7 @@
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3765,83 +3765,83 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="M26" t="n">
-        <v>3.3</v>
+        <v>3.39</v>
       </c>
       <c r="N26" t="n">
-        <v>5.75</v>
+        <v>5.31</v>
       </c>
       <c r="O26" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="P26" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="Q26" t="n">
         <v>6</v>
       </c>
       <c r="R26" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="S26" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="T26" t="n">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="U26" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="V26" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="W26" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="X26" t="n">
-        <v>2.48</v>
+        <v>2.39</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.6</v>
+        <v>2.19</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.48</v>
+        <v>1.6</v>
       </c>
       <c r="AA26" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="AB26" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>['83']</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG26" t="n">
         <v>1.14</v>
       </c>
-      <c r="AC26" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AE26" t="inlineStr">
-        <is>
-          <t>['21']</t>
-        </is>
-      </c>
-      <c r="AF26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG26" t="n">
-        <v>1.19</v>
-      </c>
       <c r="AH26" t="n">
-        <v>1.96</v>
+        <v>2.15</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AJ26" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45607.875</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Argentina Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,109 +3868,109 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Belgrano</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Instituto</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
         <v>2</v>
       </c>
-      <c r="J27" t="n">
-        <v>1</v>
-      </c>
       <c r="K27" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.6</v>
+        <v>2.91</v>
       </c>
       <c r="M27" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="N27" t="n">
-        <v>3</v>
+        <v>2.66</v>
       </c>
       <c r="O27" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="P27" t="n">
         <v>1.91</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="R27" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="S27" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="T27" t="n">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="U27" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="V27" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="W27" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="X27" t="n">
-        <v>2.49</v>
+        <v>2.45</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="Z27" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>['20', '41']</t>
+        </is>
+      </c>
+      <c r="AG27" t="n">
         <v>1.44</v>
       </c>
-      <c r="AA27" t="n">
-        <v>4.87</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AE27" t="inlineStr">
-        <is>
-          <t>['4', '36', '78']</t>
-        </is>
-      </c>
-      <c r="AF27" t="inlineStr">
-        <is>
-          <t>['22']</t>
-        </is>
-      </c>
-      <c r="AG27" t="n">
-        <v>1.35</v>
-      </c>
       <c r="AH27" t="n">
-        <v>1.6</v>
+        <v>1.42</v>
       </c>
       <c r="AI27" t="n">
-        <v>1.91</v>
+        <v>2.5</v>
       </c>
       <c r="AJ27" t="n">
-        <v>2.3</v>
+        <v>1.83</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45607.875</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Primera División</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,25 +3997,25 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Belgrano</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Instituto</t>
         </is>
       </c>
       <c r="G28" t="n">
+        <v>3</v>
+      </c>
+      <c r="H28" t="n">
         <v>1</v>
       </c>
-      <c r="H28" t="n">
-        <v>0</v>
-      </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -4023,83 +4023,83 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.7</v>
+        <v>2.6</v>
       </c>
       <c r="M28" t="n">
-        <v>3.39</v>
+        <v>3</v>
       </c>
       <c r="N28" t="n">
-        <v>5.31</v>
+        <v>3</v>
       </c>
       <c r="O28" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X28" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>4.87</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>['4', '36', '78']</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>['22']</t>
+        </is>
+      </c>
+      <c r="AG28" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AJ28" t="n">
         <v>2.3</v>
-      </c>
-      <c r="P28" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>6</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S28" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T28" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="X28" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AE28" t="inlineStr">
-        <is>
-          <t>['83']</t>
-        </is>
-      </c>
-      <c r="AF28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG28" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>3.4</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45607.875</v>
